--- a/stories/arbres/TREE-AUT-016.xlsx
+++ b/stories/arbres/TREE-AUT-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -831,6 +831,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -845,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV87"/>
+  <dimension ref="A1:AW87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1139,6 +1151,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1301,6 +1318,11 @@
         <v>12</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Aujourd'hui, Noé est avec papa, dans le salon. Noé a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé écoute papa. Noé entend les mots : manteau, sortir, rentrer.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1491,6 +1513,11 @@
         <v>12</v>
       </c>
       <c r="AV3" s="2" t="inlineStr"/>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1515,7 +1542,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tait une seconde. papa dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tait une seconde. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1653,6 +1680,12 @@
         <v>12</v>
       </c>
       <c r="AV4" s="2" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tait une seconde.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1833,6 +1866,11 @@
       <c r="AV5" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -2001,6 +2039,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2191,6 +2234,11 @@
         <v>12</v>
       </c>
       <c r="AV7" s="2" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2353,6 +2401,11 @@
         <v>12</v>
       </c>
       <c r="AV8" s="2" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2543,6 +2596,11 @@
         <v>12</v>
       </c>
       <c r="AV9" s="2" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2705,6 +2763,11 @@
         <v>12</v>
       </c>
       <c r="AV10" s="2" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2867,6 +2930,11 @@
         <v>12</v>
       </c>
       <c r="AV11" s="2" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3029,6 +3097,11 @@
         <v>12</v>
       </c>
       <c r="AV12" s="2" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3191,6 +3264,11 @@
         <v>12</v>
       </c>
       <c r="AV13" s="2" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3353,6 +3431,11 @@
         <v>12</v>
       </c>
       <c r="AV14" s="2" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3515,6 +3598,11 @@
         <v>12</v>
       </c>
       <c r="AV15" s="2" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3677,6 +3765,11 @@
         <v>12</v>
       </c>
       <c r="AV16" s="2" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3867,6 +3960,11 @@
         <v>12</v>
       </c>
       <c r="AV17" s="2" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4029,6 +4127,11 @@
         <v>12</v>
       </c>
       <c r="AV18" s="2" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4191,6 +4294,11 @@
         <v>12</v>
       </c>
       <c r="AV19" s="2" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4353,6 +4461,11 @@
         <v>12</v>
       </c>
       <c r="AV20" s="2" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la cuisine, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4515,6 +4628,11 @@
         <v>12</v>
       </c>
       <c r="AV21" s="2" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4677,6 +4795,11 @@
         <v>12</v>
       </c>
       <c r="AV22" s="2" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4839,6 +4962,11 @@
         <v>12</v>
       </c>
       <c r="AV23" s="2" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5001,6 +5129,11 @@
         <v>12</v>
       </c>
       <c r="AV24" s="2" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5191,6 +5324,11 @@
         <v>12</v>
       </c>
       <c r="AV25" s="2" t="inlineStr"/>
+      <c r="AW25" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5353,6 +5491,11 @@
         <v>12</v>
       </c>
       <c r="AV26" s="2" t="inlineStr"/>
+      <c r="AW26" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5515,6 +5658,11 @@
         <v>12</v>
       </c>
       <c r="AV27" s="2" t="inlineStr"/>
+      <c r="AW27" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5677,6 +5825,11 @@
         <v>12</v>
       </c>
       <c r="AV28" s="2" t="inlineStr"/>
+      <c r="AW28" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5839,6 +5992,11 @@
         <v>12</v>
       </c>
       <c r="AV29" s="2" t="inlineStr"/>
+      <c r="AW29" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6001,6 +6159,11 @@
         <v>12</v>
       </c>
       <c r="AV30" s="2" t="inlineStr"/>
+      <c r="AW30" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6163,6 +6326,11 @@
         <v>12</v>
       </c>
       <c r="AV31" s="2" t="inlineStr"/>
+      <c r="AW31" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6187,7 +6355,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main. papa dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6325,6 +6493,12 @@
         <v>12</v>
       </c>
       <c r="AV32" s="2" t="inlineStr"/>
+      <c r="AW32" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6505,6 +6679,11 @@
       <c r="AV33" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW33" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -6673,6 +6852,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW34" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6863,6 +7047,11 @@
         <v>12</v>
       </c>
       <c r="AV35" s="2" t="inlineStr"/>
+      <c r="AW35" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7025,6 +7214,11 @@
         <v>12</v>
       </c>
       <c r="AV36" s="2" t="inlineStr"/>
+      <c r="AW36" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7215,6 +7409,11 @@
         <v>12</v>
       </c>
       <c r="AV37" s="2" t="inlineStr"/>
+      <c r="AW37" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7377,6 +7576,11 @@
         <v>12</v>
       </c>
       <c r="AV38" s="2" t="inlineStr"/>
+      <c r="AW38" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7539,6 +7743,11 @@
         <v>12</v>
       </c>
       <c r="AV39" s="2" t="inlineStr"/>
+      <c r="AW39" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7701,6 +7910,11 @@
         <v>12</v>
       </c>
       <c r="AV40" s="2" t="inlineStr"/>
+      <c r="AW40" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. La couverture est douce. On range un objet. Cette fin-là est celle de le jardin, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7863,6 +8077,11 @@
         <v>12</v>
       </c>
       <c r="AV41" s="2" t="inlineStr"/>
+      <c r="AW41" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8025,6 +8244,11 @@
         <v>12</v>
       </c>
       <c r="AV42" s="2" t="inlineStr"/>
+      <c r="AW42" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8187,6 +8411,11 @@
         <v>12</v>
       </c>
       <c r="AV43" s="2" t="inlineStr"/>
+      <c r="AW43" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8349,6 +8578,11 @@
         <v>12</v>
       </c>
       <c r="AV44" s="2" t="inlineStr"/>
+      <c r="AW44" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8539,6 +8773,11 @@
         <v>12</v>
       </c>
       <c r="AV45" s="2" t="inlineStr"/>
+      <c r="AW45" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8701,6 +8940,11 @@
         <v>12</v>
       </c>
       <c r="AV46" s="2" t="inlineStr"/>
+      <c r="AW46" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -8863,6 +9107,11 @@
         <v>12</v>
       </c>
       <c r="AV47" s="2" t="inlineStr"/>
+      <c r="AW47" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9025,6 +9274,11 @@
         <v>12</v>
       </c>
       <c r="AV48" s="2" t="inlineStr"/>
+      <c r="AW48" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On range un objet. Cette fin-là est celle de le jardin, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9187,6 +9441,11 @@
         <v>12</v>
       </c>
       <c r="AV49" s="2" t="inlineStr"/>
+      <c r="AW49" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9349,6 +9608,11 @@
         <v>12</v>
       </c>
       <c r="AV50" s="2" t="inlineStr"/>
+      <c r="AW50" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9511,6 +9775,11 @@
         <v>12</v>
       </c>
       <c r="AV51" s="2" t="inlineStr"/>
+      <c r="AW51" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9673,6 +9942,11 @@
         <v>12</v>
       </c>
       <c r="AV52" s="2" t="inlineStr"/>
+      <c r="AW52" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -9863,6 +10137,11 @@
         <v>12</v>
       </c>
       <c r="AV53" s="2" t="inlineStr"/>
+      <c r="AW53" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10025,6 +10304,11 @@
         <v>12</v>
       </c>
       <c r="AV54" s="2" t="inlineStr"/>
+      <c r="AW54" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10187,6 +10471,11 @@
         <v>12</v>
       </c>
       <c r="AV55" s="2" t="inlineStr"/>
+      <c r="AW55" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10349,6 +10638,11 @@
         <v>12</v>
       </c>
       <c r="AV56" s="2" t="inlineStr"/>
+      <c r="AW56" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le jardin, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10511,6 +10805,11 @@
         <v>12</v>
       </c>
       <c r="AV57" s="2" t="inlineStr"/>
+      <c r="AW57" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10673,6 +10972,11 @@
         <v>12</v>
       </c>
       <c r="AV58" s="2" t="inlineStr"/>
+      <c r="AW58" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -10835,6 +11139,11 @@
         <v>12</v>
       </c>
       <c r="AV59" s="2" t="inlineStr"/>
+      <c r="AW59" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -10859,7 +11168,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet. papa dit : je suis là. On reste ensemble.</t>
+          <t>Noé va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet. Je suis là. On reste ensemble.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -10997,6 +11306,12 @@
         <v>12</v>
       </c>
       <c r="AV60" s="2" t="inlineStr"/>
+      <c r="AW60" t="inlineStr">
+        <is>
+          <t>narrateur|Noé va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet.
+papa|Je suis là. On reste ensemble.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11177,6 +11492,11 @@
       <c r="AV61" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW61" t="inlineStr">
+        <is>
+          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
     </row>
@@ -11345,6 +11665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW62" t="inlineStr">
+        <is>
+          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11535,6 +11860,11 @@
         <v>12</v>
       </c>
       <c r="AV63" s="2" t="inlineStr"/>
+      <c r="AW63" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11697,6 +12027,11 @@
         <v>12</v>
       </c>
       <c r="AV64" s="2" t="inlineStr"/>
+      <c r="AW64" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -11887,6 +12222,11 @@
         <v>12</v>
       </c>
       <c r="AV65" s="2" t="inlineStr"/>
+      <c r="AW65" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12049,6 +12389,11 @@
         <v>12</v>
       </c>
       <c r="AV66" s="2" t="inlineStr"/>
+      <c r="AW66" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12211,6 +12556,11 @@
         <v>12</v>
       </c>
       <c r="AV67" s="2" t="inlineStr"/>
+      <c r="AW67" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12373,6 +12723,11 @@
         <v>12</v>
       </c>
       <c r="AV68" s="2" t="inlineStr"/>
+      <c r="AW68" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la chambre, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12535,6 +12890,11 @@
         <v>12</v>
       </c>
       <c r="AV69" s="2" t="inlineStr"/>
+      <c r="AW69" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12697,6 +13057,11 @@
         <v>12</v>
       </c>
       <c r="AV70" s="2" t="inlineStr"/>
+      <c r="AW70" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -12859,6 +13224,11 @@
         <v>12</v>
       </c>
       <c r="AV71" s="2" t="inlineStr"/>
+      <c r="AW71" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13021,6 +13391,11 @@
         <v>12</v>
       </c>
       <c r="AV72" s="2" t="inlineStr"/>
+      <c r="AW72" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13211,6 +13586,11 @@
         <v>12</v>
       </c>
       <c r="AV73" s="2" t="inlineStr"/>
+      <c r="AW73" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13373,6 +13753,11 @@
         <v>12</v>
       </c>
       <c r="AV74" s="2" t="inlineStr"/>
+      <c r="AW74" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13535,6 +13920,11 @@
         <v>12</v>
       </c>
       <c r="AV75" s="2" t="inlineStr"/>
+      <c r="AW75" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -13697,6 +14087,11 @@
         <v>12</v>
       </c>
       <c r="AV76" s="2" t="inlineStr"/>
+      <c r="AW76" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la chambre, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -13859,6 +14254,11 @@
         <v>12</v>
       </c>
       <c r="AV77" s="2" t="inlineStr"/>
+      <c r="AW77" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14021,6 +14421,11 @@
         <v>12</v>
       </c>
       <c r="AV78" s="2" t="inlineStr"/>
+      <c r="AW78" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14183,6 +14588,11 @@
         <v>12</v>
       </c>
       <c r="AV79" s="2" t="inlineStr"/>
+      <c r="AW79" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14345,6 +14755,11 @@
         <v>12</v>
       </c>
       <c r="AV80" s="2" t="inlineStr"/>
+      <c r="AW80" t="inlineStr">
+        <is>
+          <t>narrateur|Noé a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14535,6 +14950,11 @@
         <v>12</v>
       </c>
       <c r="AV81" s="2" t="inlineStr"/>
+      <c r="AW81" t="inlineStr">
+        <is>
+          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -14697,6 +15117,11 @@
         <v>12</v>
       </c>
       <c r="AV82" s="2" t="inlineStr"/>
+      <c r="AW82" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -14859,6 +15284,11 @@
         <v>12</v>
       </c>
       <c r="AV83" s="2" t="inlineStr"/>
+      <c r="AW83" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15021,6 +15451,11 @@
         <v>12</v>
       </c>
       <c r="AV84" s="2" t="inlineStr"/>
+      <c r="AW84" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la chambre, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15183,6 +15618,11 @@
         <v>12</v>
       </c>
       <c r="AV85" s="2" t="inlineStr"/>
+      <c r="AW85" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15345,6 +15785,11 @@
         <v>12</v>
       </c>
       <c r="AV86" s="2" t="inlineStr"/>
+      <c r="AW86" t="inlineStr">
+        <is>
+          <t>narrateur|Noé rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15507,6 +15952,11 @@
         <v>12</v>
       </c>
       <c r="AV87" s="2" t="inlineStr"/>
+      <c r="AW87" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15525,7 +15975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15542,6 +15992,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-016.xlsx
+++ b/stories/arbres/TREE-AUT-016.xlsx
@@ -857,7 +857,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW87"/>
+  <dimension ref="A1:AX87"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1156,6 +1156,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1323,6 +1328,7 @@
           <t>narrateur|Aujourd'hui, Noé est avec papa, dans le salon. Noé a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé écoute papa. Noé entend les mots : manteau, sortir, rentrer.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1518,6 +1524,7 @@
           <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1686,6 +1693,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1873,6 +1881,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2044,6 +2053,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2239,6 +2249,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2406,6 +2417,7 @@
           <t>narrateur|Noé a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2601,6 +2613,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2768,6 +2781,7 @@
           <t>narrateur|Noé rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2935,6 +2949,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -3102,6 +3117,7 @@
           <t>narrateur|Noé rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3269,6 +3285,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3436,6 +3453,7 @@
           <t>narrateur|Noé rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3603,6 +3621,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3770,6 +3789,7 @@
           <t>narrateur|Noé a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3965,6 +3985,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4132,6 +4153,7 @@
           <t>narrateur|Noé rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4299,6 +4321,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4466,6 +4489,7 @@
           <t>narrateur|Noé rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la cuisine, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4633,6 +4657,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4800,6 +4825,7 @@
           <t>narrateur|Noé rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4967,6 +4993,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5134,6 +5161,7 @@
           <t>narrateur|Noé a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5329,6 +5357,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5496,6 +5525,7 @@
           <t>narrateur|Noé rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5663,6 +5693,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5830,6 +5861,7 @@
           <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5997,6 +6029,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6164,6 +6197,7 @@
           <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6331,6 +6365,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6499,6 +6534,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6686,6 +6722,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6857,6 +6894,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -7052,6 +7090,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7219,6 +7258,7 @@
           <t>narrateur|Noé a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7414,6 +7454,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7581,6 +7622,7 @@
           <t>narrateur|Noé rejoint le matin. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7748,6 +7790,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7915,6 +7958,7 @@
           <t>narrateur|Noé rejoint après la sieste. La couverture est douce. On range un objet. Cette fin-là est celle de le jardin, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -8082,6 +8126,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8249,6 +8294,7 @@
           <t>narrateur|Noé rejoint le soir. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8416,6 +8462,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8583,6 +8630,7 @@
           <t>narrateur|Noé a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8778,6 +8826,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8945,6 +8994,7 @@
           <t>narrateur|Noé rejoint le matin. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9112,6 +9162,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9279,6 +9330,7 @@
           <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On range un objet. Cette fin-là est celle de le jardin, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9446,6 +9498,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9613,6 +9666,7 @@
           <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9780,6 +9834,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9947,6 +10002,7 @@
           <t>narrateur|Noé a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10142,6 +10198,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10309,6 +10366,7 @@
           <t>narrateur|Noé rejoint le matin. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10476,6 +10534,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10643,6 +10702,7 @@
           <t>narrateur|Noé rejoint après la sieste. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le jardin, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10810,6 +10870,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10977,6 +11038,7 @@
           <t>narrateur|Noé rejoint le soir. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11144,6 +11206,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11312,6 +11375,7 @@
 papa|Je suis là. On reste ensemble.</t>
         </is>
       </c>
+      <c r="AX60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11499,6 +11563,7 @@
           <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
         </is>
       </c>
+      <c r="AX61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11670,6 +11735,7 @@
           <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
         </is>
       </c>
+      <c r="AX62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11865,6 +11931,7 @@
           <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
+      <c r="AX63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -12032,6 +12099,7 @@
           <t>narrateur|Noé a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12227,6 +12295,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12394,6 +12463,7 @@
           <t>narrateur|Noé rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12561,6 +12631,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12728,6 +12799,7 @@
           <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la chambre, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12895,6 +12967,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -13062,6 +13135,7 @@
           <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13229,6 +13303,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13396,6 +13471,7 @@
           <t>narrateur|Noé a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13591,6 +13667,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13758,6 +13835,7 @@
           <t>narrateur|Noé rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13925,6 +14003,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14092,6 +14171,7 @@
           <t>narrateur|Noé rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la chambre, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14259,6 +14339,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14426,6 +14507,7 @@
           <t>narrateur|Noé rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14593,6 +14675,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14760,6 +14843,7 @@
           <t>narrateur|Noé a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
         </is>
       </c>
+      <c r="AX80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14955,6 +15039,7 @@
           <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
+      <c r="AX81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15122,6 +15207,7 @@
           <t>narrateur|Noé rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15289,6 +15375,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15456,6 +15543,7 @@
           <t>narrateur|Noé rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la chambre, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15623,6 +15711,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15790,6 +15879,7 @@
           <t>narrateur|Noé rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
         </is>
       </c>
+      <c r="AX86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15957,6 +16047,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX87" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -15975,7 +16066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -15999,6 +16090,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -16013,7 +16118,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -16200,6 +16305,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/TREE-AUT-016.xlsx
+++ b/stories/arbres/TREE-AUT-016.xlsx
@@ -489,7 +489,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -552,7 +552,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Prendre son manteau avant de sortir — dans le salon</t>
+          <t>Le manteau de Raphaël dans le salon</t>
         </is>
       </c>
     </row>
@@ -843,6 +843,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Raphaël a envie de sortir. Dans le salon, le manteau de laine attend sur le petit crochet. Avant chaque sortie, il le prend. En rentrant, il le raccroche.</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1197,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Aujourd'hui, Noé est avec papa, dans le salon. Noé a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé écoute papa. Noé entend les mots : manteau, sortir, rentrer.</t>
+          <t>Le radiateur du salon fait tic tic. Un manteau de laine attend. Il est sur le petit crochet. Le crochet est bas, tout près. La pluie trace des lignes. Elles glissent sur la grande vitre. Le tapis beige est tout épais. Une chaussette dépasse sous le canapé. L'air sent la terre mouillée. La fenêtre est un peu ouverte. Les bottes jaunes sont là. Elles sont dans une flaque de lumière. Raphaël, on va sortir. Tu prends ton manteau avant. Le manteau est sur le crochet. Il est à ta hauteur. En ce moment, Raphaël est dans le salon. Il a envie de jouer dehors. Il va vers le crochet. Il prend le manteau. Le tissu est un peu rêche. Il glisse un bras. Il glisse l'autre bras. Le manteau est chaud. Bravo. Tu as pris le manteau. On sort. Puis on rentre. Et on raccroche le manteau. J'ai mon manteau.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1325,10 +1337,36 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Aujourd'hui, Noé est avec papa, dans le salon. Noé a envie de jouer. papa est là, tout près. On va apprendre : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé écoute papa. Noé entend les mots : manteau, sortir, rentrer.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|Le radiateur du salon fait tic tic.
+narrateur|Un manteau de laine attend.
+narrateur|Il est sur le petit crochet.
+narrateur|Le crochet est bas, tout près.
+narrateur|La pluie trace des lignes.
+narrateur|Elles glissent sur la grande vitre.
+narrateur|Le tapis beige est tout épais.
+narrateur|Une chaussette dépasse sous le canapé.
+narrateur|L'air sent la terre mouillée.
+narrateur|La fenêtre est un peu ouverte.
+narrateur|Les bottes jaunes sont là.
+narrateur|Elles sont dans une flaque de lumière.
+papa|Raphaël, on va sortir.
+papa|Tu prends ton manteau avant.
+maman|Le manteau est sur le crochet.
+maman|Il est à ta hauteur.
+narrateur|En ce moment, Raphaël est dans le salon.
+narrateur|Il a envie de jouer dehors.
+narrateur|Il va vers le crochet.
+narrateur|Il prend le manteau.
+narrateur|Le tissu est un peu rêche.
+narrateur|Il glisse un bras.
+narrateur|Il glisse l'autre bras.
+narrateur|Le manteau est chaud.
+maman|Bravo. Tu as pris le manteau.
+papa|On sort. Puis on rentre.
+papa|Et on raccroche le manteau.
+enfant-m|J'ai mon manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1353,7 +1391,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>On passe où, avant de sortir ? On peut prendre la cuisine, le jardin, ou la chambre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1521,10 +1559,10 @@
       <c r="AV3" s="2" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>papa|On passe où, avant de sortir ?
+narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1549,7 +1587,7 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tait une seconde. Je suis là. On reste ensemble.</t>
+          <t>Raphaël va vers la cuisine. Les carreaux sont un peu tièdes. Ça sent la soupe dans la casserole. La vitre de la cuisine est embuée. Le manteau est déjà sur Raphaël. Avant de sortir, on prend le manteau. Tu l'as pris. Bravo. Il est chaud. Une feuille de laurier tombe près de l'évier. On sort. Puis on rentre. Et on raccroche. Raphaël touche le bouton du manteau.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
@@ -1689,11 +1727,20 @@
       <c r="AV4" s="2" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Noé va vers la cuisine. Une feuille tombe. papa sourit. Ici, c'est la cuisine. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tait une seconde.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Raphaël va vers la cuisine.
+narrateur|Les carreaux sont un peu tièdes.
+narrateur|Ça sent la soupe dans la casserole.
+narrateur|La vitre de la cuisine est embuée.
+narrateur|Le manteau est déjà sur Raphaël.
+papa|Avant de sortir, on prend le manteau.
+maman|Tu l'as pris. Bravo.
+enfant-m|Il est chaud.
+narrateur|Une feuille de laurier tombe près de l'évier.
+papa|On sort. Puis on rentre.
+papa|Et on raccroche.
+narrateur|Raphaël touche le bouton du manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1718,7 +1765,7 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Avant de sortir, que prend-on ?</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -1878,10 +1925,9 @@
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Avant de sortir, que prend-on ?</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1906,7 +1952,7 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau. Bravo. Tu as pris le manteau. En rentrant, on le raccroche. Raphaël respire. Ça sent la soupe.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2050,10 +2096,12 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Oui. On prend le manteau.
+papa|Bravo. Tu as pris le manteau.
+maman|En rentrant, on le raccroche.
+narrateur|Raphaël respire. Ça sent la soupe.</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -2078,7 +2126,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu emportes quel jeu ? On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2246,10 +2294,10 @@
       <c r="AV7" s="2" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr"/>
+          <t>maman|Tu emportes quel jeu ?
+narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -2274,7 +2322,7 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
+          <t>Raphaël a choisi les cubes. Ils sont en bois. Ils cliquent. Un vélo passe au loin. On prend les cubes. Et le manteau reste mis. Tu as ton manteau ? Oui. Il est chaud. Bravo. On sort. Puis on rentre. Les cubes sont dans une boîte lisse.</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
@@ -2414,10 +2462,21 @@
       <c r="AV8" s="2" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi les cubes. Un vélo passe au loin. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX8" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi les cubes.
+narrateur|Ils sont en bois. Ils cliquent.
+narrateur|Un vélo passe au loin.
+papa|On prend les cubes. Et le manteau reste mis.
+maman|Tu as ton manteau ?
+enfant-m|Oui. Il est chaud.
+papa|Bravo. On sort. Puis on rentre.
+narrateur|Les cubes sont dans une boîte lisse.</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>voiture_passe</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -2442,7 +2501,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2610,10 +2669,10 @@
       <c r="AV9" s="2" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX9" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -2638,7 +2697,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2778,10 +2837,23 @@
       <c r="AV10" s="2" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. Un chat miaule une fois. On se tait une seconde. Cette fin-là est celle de la cuisine, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -2806,7 +2878,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -2946,10 +3018,16 @@
       <c r="AV11" s="2" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -2974,7 +3052,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3114,10 +3192,23 @@
       <c r="AV12" s="2" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de la cuisine, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -3142,7 +3233,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3282,10 +3373,16 @@
       <c r="AV13" s="2" t="inlineStr"/>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX13" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -3310,7 +3407,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3450,10 +3547,23 @@
       <c r="AV14" s="2" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. La couverture est douce. On range un objet. Cette fin-là est celle de la cuisine, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX14" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -3478,7 +3588,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3618,10 +3728,16 @@
       <c r="AV15" s="2" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX15" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -3646,7 +3762,7 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>Raphaël a choisi le livre. Les pages sentent le papier. La lumière de la cuisine est claire. Le livre vient. Le manteau aussi. Tu as pris le manteau avant de sortir. Oui, papa. Bravo. En rentrant, on raccroche. Raphaël souffle sur une page.</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
@@ -3786,10 +3902,16 @@
       <c r="AV16" s="2" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le livre. La lumière est claire. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX16" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi le livre.
+narrateur|Les pages sentent le papier.
+narrateur|La lumière de la cuisine est claire.
+maman|Le livre vient. Le manteau aussi.
+papa|Tu as pris le manteau avant de sortir.
+enfant-m|Oui, papa.
+maman|Bravo. En rentrant, on raccroche.
+narrateur|Raphaël souffle sur une page.</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -3814,7 +3936,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -3982,10 +4104,10 @@
       <c r="AV17" s="2" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX17" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -4010,7 +4132,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4150,10 +4272,23 @@
       <c r="AV18" s="2" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. Les chaussures font toc toc. On se tait une seconde. Cette fin-là est celle de la cuisine, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX18" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -4178,7 +4313,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4318,10 +4453,16 @@
       <c r="AV19" s="2" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX19" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -4346,7 +4487,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la cuisine, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4486,10 +4627,23 @@
       <c r="AV20" s="2" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. La couverture est douce. On se tient la main. Cette fin-là est celle de la cuisine, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX20" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -4514,7 +4668,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4654,10 +4808,16 @@
       <c r="AV21" s="2" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX21" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -4682,7 +4842,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4822,10 +4982,23 @@
       <c r="AV22" s="2" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. On entend un oiseau. On range un objet. Cette fin-là est celle de la cuisine, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -4850,7 +5023,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -4990,10 +5163,16 @@
       <c r="AV23" s="2" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX23" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -5018,7 +5197,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Raphaël a choisi la dînette. Les petites tasses sont lisses. Ça sent encore la soupe. On emporte la dînette. Le manteau est bien mis. Bravo. Je sors avec. Puis on rentre. On raccroche le manteau. Une tasse fait un tout petit ting.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5158,10 +5337,16 @@
       <c r="AV24" s="2" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi la dînette. Il y a des miettes sur la table. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX24" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi la dînette.
+narrateur|Les petites tasses sont lisses.
+narrateur|Ça sent encore la soupe.
+papa|On emporte la dînette.
+maman|Le manteau est bien mis. Bravo.
+enfant-m|Je sors avec.
+papa|Puis on rentre. On raccroche le manteau.
+narrateur|Une tasse fait un tout petit ting.</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -5186,7 +5371,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5354,10 +5539,10 @@
       <c r="AV25" s="2" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX25" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -5382,7 +5567,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5522,10 +5707,23 @@
       <c r="AV26" s="2" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. La couverture est douce. On se tait une seconde. Cette fin-là est celle de la cuisine, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX26" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -5550,7 +5748,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5690,10 +5888,16 @@
       <c r="AV27" s="2" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX27" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -5718,7 +5922,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -5858,10 +6062,23 @@
       <c r="AV28" s="2" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On se tient la main. Cette fin-là est celle de la cuisine, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX28" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -5886,7 +6103,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6026,10 +6243,16 @@
       <c r="AV29" s="2" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX29" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -6054,7 +6277,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6194,10 +6417,23 @@
       <c r="AV30" s="2" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la cuisine, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX30" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|La cuisine sent encore la soupe.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -6222,7 +6458,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6362,10 +6598,16 @@
       <c r="AV31" s="2" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX31" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la cuisine.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -6390,7 +6632,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main. Je suis là. On reste ensemble.</t>
+          <t>Raphaël va vers le jardin. L'herbe est mouillée, toute brillante. L'air est frais sur le nez. Le manteau sent la laine. On a pris le manteau avant de sortir. Bravo, Raphaël. J'ai pas froid. Une goutte tombe d'une feuille. Elle fait un tout petit bruit. Quand on rentre, on raccroche le manteau. Raphaël serre le col contre sa joue.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6530,11 +6772,19 @@
       <c r="AV32" s="2" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>narrateur|Noé va vers le jardin. L'eau coule, tout petit bruit. papa sourit. Ici, c'est le jardin. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On se tient la main.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX32" t="inlineStr"/>
+          <t>narrateur|Raphaël va vers le jardin.
+narrateur|L'herbe est mouillée, toute brillante.
+narrateur|L'air est frais sur le nez.
+narrateur|Le manteau sent la laine.
+papa|On a pris le manteau avant de sortir.
+maman|Bravo, Raphaël.
+enfant-m|J'ai pas froid.
+narrateur|Une goutte tombe d'une feuille.
+narrateur|Elle fait un tout petit bruit.
+papa|Quand on rentre, on raccroche le manteau.
+narrateur|Raphaël serre le col contre sa joue.</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -6559,7 +6809,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Avant de sortir, que prend-on ?</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -6719,10 +6969,9 @@
       </c>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
-        </is>
-      </c>
-      <c r="AX33" t="inlineStr"/>
+          <t>narrateur|Avant de sortir, que prend-on ?</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -6747,7 +6996,7 @@
       </c>
       <c r="E34" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. On prend le manteau avant de sortir. Bravo, Raphaël. Bon travail. Puis on rentre. On raccroche. L'herbe mouillée brille encore.</t>
         </is>
       </c>
       <c r="F34" s="2" t="inlineStr">
@@ -6891,10 +7140,12 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX34" t="inlineStr"/>
+          <t>narrateur|Oui. On prend le manteau avant de sortir.
+maman|Bravo, Raphaël. Bon travail.
+papa|Puis on rentre. On raccroche.
+narrateur|L'herbe mouillée brille encore.</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -6919,7 +7170,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu emportes quel jeu ? On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7087,10 +7338,10 @@
       <c r="AV35" s="2" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
-        </is>
-      </c>
-      <c r="AX35" t="inlineStr"/>
+          <t>maman|Tu emportes quel jeu ?
+narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -7115,7 +7366,7 @@
       </c>
       <c r="E36" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
+          <t>Raphaël a choisi les cubes, dans le jardin. Un chat miaule une fois. Les cubes sont un peu froids. On joue. Le manteau reste sur toi. Tu l'as pris avant de sortir. Bravo. Les cubes font clic. Quand on rentre, on raccroche. L'herbe mouille le bas du manteau.</t>
         </is>
       </c>
       <c r="F36" s="2" t="inlineStr">
@@ -7255,10 +7506,16 @@
       <c r="AV36" s="2" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi les cubes. Un chat miaule une fois. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX36" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi les cubes, dans le jardin.
+narrateur|Un chat miaule une fois.
+narrateur|Les cubes sont un peu froids.
+papa|On joue. Le manteau reste sur toi.
+maman|Tu l'as pris avant de sortir. Bravo.
+enfant-m|Les cubes font clic.
+papa|Quand on rentre, on raccroche.
+narrateur|L'herbe mouille le bas du manteau.</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -7283,7 +7540,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7451,10 +7708,10 @@
       <c r="AV37" s="2" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX37" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="inlineStr">
@@ -7479,7 +7736,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7619,10 +7876,23 @@
       <c r="AV38" s="2" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. Les chaussures font toc toc. On se tient la main. Cette fin-là est celle de le jardin, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX38" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="inlineStr">
@@ -7647,7 +7917,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -7787,10 +8057,16 @@
       <c r="AV39" s="2" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX39" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" s="2" t="inlineStr">
@@ -7815,7 +8091,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. La couverture est douce. On range un objet. Cette fin-là est celle de le jardin, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -7955,10 +8231,23 @@
       <c r="AV40" s="2" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. La couverture est douce. On range un objet. Cette fin-là est celle de le jardin, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX40" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="inlineStr">
@@ -7983,7 +8272,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8123,10 +8412,16 @@
       <c r="AV41" s="2" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX41" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" s="2" t="inlineStr">
@@ -8151,7 +8446,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8291,10 +8586,23 @@
       <c r="AV42" s="2" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. On entend un oiseau. On dit merci. Cette fin-là est celle de le jardin, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX42" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="inlineStr">
@@ -8319,7 +8627,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8459,10 +8767,16 @@
       <c r="AV43" s="2" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX43" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="inlineStr">
@@ -8487,7 +8801,7 @@
       </c>
       <c r="E44" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>Raphaël a choisi le livre, dehors. Une goutte tombe sur la couverture. On met le livre à l'abri. Le manteau te tient chaud. Il est rêche et chaud. Bravo. Tu as pris le manteau. On rentre bientôt. On raccroche. Raphaël tient le livre contre lui.</t>
         </is>
       </c>
       <c r="F44" s="2" t="inlineStr">
@@ -8627,10 +8941,16 @@
       <c r="AV44" s="2" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le livre. Les chaussures font toc toc. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX44" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi le livre, dehors.
+narrateur|Une goutte tombe sur la couverture.
+maman|On met le livre à l'abri.
+papa|Le manteau te tient chaud.
+enfant-m|Il est rêche et chaud.
+maman|Bravo. Tu as pris le manteau.
+papa|On rentre bientôt. On raccroche.
+narrateur|Raphaël tient le livre contre lui.</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="inlineStr">
@@ -8655,7 +8975,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -8823,10 +9143,10 @@
       <c r="AV45" s="2" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX45" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="inlineStr">
@@ -8851,7 +9171,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -8991,10 +9311,23 @@
       <c r="AV46" s="2" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. La couverture est douce. On se tient la main. Cette fin-là est celle de le jardin, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX46" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="inlineStr">
@@ -9019,7 +9352,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9159,10 +9492,16 @@
       <c r="AV47" s="2" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX47" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="inlineStr">
@@ -9187,7 +9526,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. On entend un oiseau. On range un objet. Cette fin-là est celle de le jardin, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9327,10 +9666,23 @@
       <c r="AV48" s="2" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On range un objet. Cette fin-là est celle de le jardin, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX48" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="inlineStr">
@@ -9355,7 +9707,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9495,10 +9847,16 @@
       <c r="AV49" s="2" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX49" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="inlineStr">
@@ -9523,7 +9881,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -9663,10 +10021,23 @@
       <c r="AV50" s="2" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de le jardin, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX50" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="inlineStr">
@@ -9691,7 +10062,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -9831,10 +10202,16 @@
       <c r="AV51" s="2" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX51" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="inlineStr">
@@ -9859,7 +10236,7 @@
       </c>
       <c r="E52" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Raphaël a choisi la dînette, dans l'herbe. Les petites assiettes sont froides. On fait un goûter de jardin. Tu as ton manteau. C'est bien. Je sers l'eau. Bravo. Après, on rentre. Et on raccroche le manteau. Une tasse tremble dans l'herbe.</t>
         </is>
       </c>
       <c r="F52" s="2" t="inlineStr">
@@ -9999,10 +10376,16 @@
       <c r="AV52" s="2" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi la dînette. La couverture est douce. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX52" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi la dînette, dans l'herbe.
+narrateur|Les petites assiettes sont froides.
+papa|On fait un goûter de jardin.
+maman|Tu as ton manteau. C'est bien.
+enfant-m|Je sers l'eau.
+papa|Bravo. Après, on rentre.
+maman|Et on raccroche le manteau.
+narrateur|Une tasse tremble dans l'herbe.</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="inlineStr">
@@ -10027,7 +10410,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10195,10 +10578,10 @@
       <c r="AV53" s="2" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX53" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="inlineStr">
@@ -10223,7 +10606,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10363,10 +10746,23 @@
       <c r="AV54" s="2" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. On entend un oiseau. On se tient la main. Cette fin-là est celle de le jardin, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX54" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="inlineStr">
@@ -10391,7 +10787,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10531,10 +10927,16 @@
       <c r="AV55" s="2" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX55" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" s="2" t="inlineStr">
@@ -10559,7 +10961,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le jardin, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -10699,10 +11101,23 @@
       <c r="AV56" s="2" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de le jardin, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX56" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="inlineStr">
@@ -10727,7 +11142,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -10867,10 +11282,16 @@
       <c r="AV57" s="2" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX57" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="inlineStr">
@@ -10895,7 +11316,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11035,10 +11456,23 @@
       <c r="AV58" s="2" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. Le vent est doux. On dit merci. Cette fin-là est celle de le jardin, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX58" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|L'herbe du jardin brille dans la lumière.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" s="2" t="inlineStr">
@@ -11063,7 +11497,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11203,10 +11637,16 @@
       <c r="AV59" s="2" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX59" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par le jardin.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="inlineStr">
@@ -11231,7 +11671,7 @@
       </c>
       <c r="E60" s="2" t="inlineStr">
         <is>
-          <t>Noé va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet. Je suis là. On reste ensemble.</t>
+          <t>Raphaël va vers la chambre. La couverture est douce, toute pliée. Le rideau bouge un peu. Le manteau frotte la porte. Tu as pris le manteau. C'est bien. Avant de sortir, on le met. Il est sur moi. L'oreiller sent le savon. On sort un moment. Puis on rentre. Et on raccroche. Raphaël marche tout doux sur le tapis.</t>
         </is>
       </c>
       <c r="F60" s="2" t="inlineStr">
@@ -11371,11 +11811,19 @@
       <c r="AV60" s="2" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>narrateur|Noé va vers la chambre. Un vélo passe au loin. papa sourit. Ici, c'est la chambre. Ce n'est pas comme les autres endroits. Noé se souvient : manteau, sortir, rentrer. Voici le geste : prendre le manteau ; le raccrocher. On range un objet.
-papa|Je suis là. On reste ensemble.</t>
-        </is>
-      </c>
-      <c r="AX60" t="inlineStr"/>
+          <t>narrateur|Raphaël va vers la chambre.
+narrateur|La couverture est douce, toute pliée.
+narrateur|Le rideau bouge un peu.
+narrateur|Le manteau frotte la porte.
+maman|Tu as pris le manteau. C'est bien.
+papa|Avant de sortir, on le met.
+enfant-m|Il est sur moi.
+narrateur|L'oreiller sent le savon.
+papa|On sort un moment.
+maman|Puis on rentre. Et on raccroche.
+narrateur|Raphaël marche tout doux sur le tapis.</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="inlineStr">
@@ -11400,7 +11848,7 @@
       </c>
       <c r="E61" s="2" t="inlineStr">
         <is>
-          <t>Que fait-on ? Prendre son manteau avant de sortir.</t>
+          <t>Avant de sortir, que prend-on ?</t>
         </is>
       </c>
       <c r="F61" s="2" t="inlineStr">
@@ -11560,10 +12008,9 @@
       </c>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>narrateur|Que fait-on ? Prendre son manteau avant de sortir.</t>
-        </is>
-      </c>
-      <c r="AX61" t="inlineStr"/>
+          <t>narrateur|Avant de sortir, que prend-on ?</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" s="2" t="inlineStr">
@@ -11588,7 +12035,7 @@
       </c>
       <c r="E62" s="2" t="inlineStr">
         <is>
-          <t>Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
+          <t>Oui. Raphaël a pris le manteau. C'est ça. Bravo. Le manteau se raccroche, en rentrant. La chambre est calme. Le rideau se tait.</t>
         </is>
       </c>
       <c r="F62" s="2" t="inlineStr">
@@ -11732,10 +12179,12 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Voici le geste : prendre le manteau ; le raccrocher. Noé respire. Noé retient : manteau, sortir, rentrer. On continue, avec papa.</t>
-        </is>
-      </c>
-      <c r="AX62" t="inlineStr"/>
+          <t>narrateur|Oui. Raphaël a pris le manteau.
+papa|C'est ça. Bravo.
+maman|Le manteau se raccroche, en rentrant.
+narrateur|La chambre est calme. Le rideau se tait.</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="inlineStr">
@@ -11760,7 +12209,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu emportes quel jeu ? On peut prendre les cubes, le livre, ou la dînette.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -11928,10 +12377,10 @@
       <c r="AV63" s="2" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
-        </is>
-      </c>
-      <c r="AX63" t="inlineStr"/>
+          <t>maman|Tu emportes quel jeu ?
+narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="inlineStr">
@@ -11956,7 +12405,7 @@
       </c>
       <c r="E64" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
+          <t>Raphaël a choisi les cubes, dans la chambre. Ils cliquent sur le tapis épais. On joue un peu. Puis on sort. Avant de sortir, le manteau est mis. Il est déjà sur moi. Bravo, Raphaël. En rentrant, on le raccroche. Un cube rouge roule sous le lit.</t>
         </is>
       </c>
       <c r="F64" s="2" t="inlineStr">
@@ -12096,10 +12545,16 @@
       <c r="AV64" s="2" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi les cubes. On entend un oiseau. Les cubes reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On dit merci. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX64" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi les cubes, dans la chambre.
+narrateur|Ils cliquent sur le tapis épais.
+maman|On joue un peu. Puis on sort.
+papa|Avant de sortir, le manteau est mis.
+enfant-m|Il est déjà sur moi.
+maman|Bravo, Raphaël.
+papa|En rentrant, on le raccroche.
+narrateur|Un cube rouge roule sous le lit.</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="inlineStr">
@@ -12124,7 +12579,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12292,10 +12747,10 @@
       <c r="AV65" s="2" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX65" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" s="2" t="inlineStr">
@@ -12320,7 +12775,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12460,10 +12915,23 @@
       <c r="AV66" s="2" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. La couverture est douce. On range un objet. Cette fin-là est celle de la chambre, les cubes et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX66" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="inlineStr">
@@ -12488,7 +12956,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -12628,10 +13096,16 @@
       <c r="AV67" s="2" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX67" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="inlineStr">
@@ -12656,7 +13130,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la chambre, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -12796,10 +13270,23 @@
       <c r="AV68" s="2" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. On entend un oiseau. On dit merci. Cette fin-là est celle de la chambre, les cubes et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX68" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="inlineStr">
@@ -12824,7 +13311,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -12964,10 +13451,16 @@
       <c r="AV69" s="2" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX69" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" s="2" t="inlineStr">
@@ -12992,7 +13485,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13132,10 +13625,23 @@
       <c r="AV70" s="2" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. Ça sent le pain chaud. On souffle doucement. Cette fin-là est celle de la chambre, les cubes et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX70" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les cubes sont rangés dans la boîte.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="inlineStr">
@@ -13160,7 +13666,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13300,10 +13806,16 @@
       <c r="AV71" s="2" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX71" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec les cubes.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="inlineStr">
@@ -13328,7 +13840,7 @@
       </c>
       <c r="E72" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
+          <t>Raphaël a choisi le livre, sur le lit. La couverture est douce sous le livre. On lit. Puis on sort. Tu as pris le manteau. Bravo. Les pages font frou frou. On rentre après. On raccroche. Raphaël touche une image lisse.</t>
         </is>
       </c>
       <c r="F72" s="2" t="inlineStr">
@@ -13468,10 +13980,15 @@
       <c r="AV72" s="2" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi le livre. Ça sent le pain chaud. Le livre reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On souffle doucement. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX72" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi le livre, sur le lit.
+narrateur|La couverture est douce sous le livre.
+papa|On lit. Puis on sort.
+maman|Tu as pris le manteau. Bravo.
+enfant-m|Les pages font frou frou.
+papa|On rentre après. On raccroche.
+narrateur|Raphaël touche une image lisse.</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="inlineStr">
@@ -13496,7 +14013,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -13664,10 +14181,10 @@
       <c r="AV73" s="2" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX73" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="inlineStr">
@@ -13692,7 +14209,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -13832,10 +14349,23 @@
       <c r="AV74" s="2" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. On entend un oiseau. On range un objet. Cette fin-là est celle de la chambre, le livre et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX74" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="inlineStr">
@@ -13860,7 +14390,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14000,10 +14530,16 @@
       <c r="AV75" s="2" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX75" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="inlineStr">
@@ -14028,7 +14564,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la chambre, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14168,10 +14704,23 @@
       <c r="AV76" s="2" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. Ça sent le pain chaud. On dit merci. Cette fin-là est celle de la chambre, le livre et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX76" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" s="2" t="inlineStr">
@@ -14196,7 +14745,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14336,10 +14885,16 @@
       <c r="AV77" s="2" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX77" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="inlineStr">
@@ -14364,7 +14919,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -14504,10 +15059,23 @@
       <c r="AV78" s="2" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. Le vent est doux. On souffle doucement. Cette fin-là est celle de la chambre, le livre et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX78" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Le livre est fermé, tout sage.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="inlineStr">
@@ -14532,7 +15100,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -14672,10 +15240,16 @@
       <c r="AV79" s="2" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX79" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec le livre.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="inlineStr">
@@ -14700,7 +15274,7 @@
       </c>
       <c r="E80" s="2" t="inlineStr">
         <is>
-          <t>Noé a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
+          <t>Raphaël a choisi la dînette, près de l'armoire. Les tasses sont alignées, toutes petites. On sert le thé. Puis on sort. Le manteau est prêt. Il est sur toi. Je sers papa. Bravo. Tu as pris le manteau. Après, on rentre. On raccroche. Ça sent le bois de l'armoire.</t>
         </is>
       </c>
       <c r="F80" s="2" t="inlineStr">
@@ -14840,10 +15414,16 @@
       <c r="AV80" s="2" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>narrateur|Noé a choisi la dînette. Le vent est doux. La dînette reste à sa place, près de papa. papa montre le geste, lentement. Voici le geste : prendre le manteau ; le raccrocher. Noé répète tout bas : manteau, sortir, rentrer. On écoute jusqu'au bout. maman n'est pas loin.</t>
-        </is>
-      </c>
-      <c r="AX80" t="inlineStr"/>
+          <t>narrateur|Raphaël a choisi la dînette, près de l'armoire.
+narrateur|Les tasses sont alignées, toutes petites.
+maman|On sert le thé. Puis on sort.
+papa|Le manteau est prêt. Il est sur toi.
+enfant-m|Je sers papa.
+maman|Bravo. Tu as pris le manteau.
+papa|Après, on rentre. On raccroche.
+narrateur|Ça sent le bois de l'armoire.</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="inlineStr">
@@ -14868,7 +15448,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15036,10 +15616,10 @@
       <c r="AV81" s="2" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
-        </is>
-      </c>
-      <c r="AX81" t="inlineStr"/>
+          <t>papa|C'est quel moment, pour sortir ?
+narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="inlineStr">
@@ -15064,7 +15644,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15204,10 +15784,23 @@
       <c r="AV82" s="2" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le matin. Ça sent le pain chaud. On range un objet. Cette fin-là est celle de la chambre, la dînette et le matin. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX82" t="inlineStr"/>
+          <t>narrateur|C'est le matin.
+narrateur|La lumière est pâle, tout douce.
+narrateur|Un oiseau chante une fois.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="inlineStr">
@@ -15232,7 +15825,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15372,10 +15965,16 @@
       <c r="AV83" s="2" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX83" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le matin.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="inlineStr">
@@ -15400,7 +15999,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la chambre, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -15540,10 +16139,23 @@
       <c r="AV84" s="2" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint après la sieste. Le vent est doux. On dit merci. Cette fin-là est celle de la chambre, la dînette et après la sieste. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX84" t="inlineStr"/>
+          <t>narrateur|C'est après la sieste.
+narrateur|Les joues de Raphaël sont chaudes.
+narrateur|La maison est encore calme.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="inlineStr">
@@ -15568,7 +16180,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -15708,10 +16320,16 @@
       <c r="AV85" s="2" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX85" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était après la sieste.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="inlineStr">
@@ -15736,7 +16354,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>Noé rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -15876,10 +16494,23 @@
       <c r="AV86" s="2" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>narrateur|Noé rejoint le soir. Le sol est un peu froid. On souffle doucement. Cette fin-là est celle de la chambre, la dînette et le soir. Noé a appris : Prendre son manteau avant de sortir. Voici le geste : prendre le manteau ; le raccrocher. Noé a entendu : manteau, sortir, rentrer. Noé dit merci à papa. On rentre.</t>
-        </is>
-      </c>
-      <c r="AX86" t="inlineStr"/>
+          <t>narrateur|C'est le soir.
+narrateur|La lampe fait un rond orange.
+narrateur|Les ombres sont longues sur le tapis.
+papa|On sort. Tu as ton manteau ?
+enfant-m|Oui. Je l'ai pris.
+maman|Bravo. C'est le bon geste.
+narrateur|Ils sortent un moment.
+narrateur|L'air touche le nez de Raphaël.
+papa|C'est l'heure de rentrer.
+narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Il le raccroche au petit crochet.
+maman|Le manteau est à sa place. Bravo.
+narrateur|Les tasses de la dînette sont empilées.
+narrateur|La chambre garde l'odeur de l'oreiller.
+papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" s="2" t="inlineStr">
@@ -15904,7 +16535,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16044,10 +16675,16 @@
       <c r="AV87" s="2" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX87" t="inlineStr"/>
+          <t>narrateur|Raphaël est passé par la chambre.
+narrateur|Il a joué avec la dînette.
+narrateur|C'était le soir.
+narrateur|Il a pris le manteau avant de sortir.
+narrateur|En rentrant, il l'a raccroché.
+maman|Le crochet attend déjà demain.
+papa|Bravo. On est rentrés.
+narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV87"/>
@@ -16066,7 +16703,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16104,6 +16741,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/TREE-AUT-016.xlsx
+++ b/stories/arbres/TREE-AUT-016.xlsx
@@ -1361,8 +1361,10 @@
 narrateur|Il glisse un bras.
 narrateur|Il glisse l'autre bras.
 narrateur|Le manteau est chaud.
-maman|Bravo. Tu as pris le manteau.
-papa|On sort. Puis on rentre.
+maman|Bravo.
+maman|Tu as pris le manteau.
+papa|On sort.
+papa|Puis on rentre.
 papa|Et on raccroche le manteau.
 enfant-m|J'ai mon manteau.</t>
         </is>
@@ -1391,7 +1393,7 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>On passe où, avant de sortir ? On peut prendre la cuisine, le jardin, ou la chambre.</t>
+          <t>On passe où, avant de sortir ? La cuisine. Le jardin. Ou la chambre.</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
@@ -1560,7 +1562,9 @@
       <c r="AW3" t="inlineStr">
         <is>
           <t>papa|On passe où, avant de sortir ?
-narrateur|On peut prendre la cuisine, le jardin, ou la chambre.</t>
+narrateur|La cuisine.
+narrateur|Le jardin.
+narrateur|Ou la chambre.</t>
         </is>
       </c>
     </row>
@@ -1733,10 +1737,12 @@
 narrateur|La vitre de la cuisine est embuée.
 narrateur|Le manteau est déjà sur Raphaël.
 papa|Avant de sortir, on prend le manteau.
-maman|Tu l'as pris. Bravo.
+maman|Tu l'as pris.
+maman|Bravo.
 enfant-m|Il est chaud.
 narrateur|Une feuille de laurier tombe près de l'évier.
-papa|On sort. Puis on rentre.
+papa|On sort.
+papa|Puis on rentre.
 papa|Et on raccroche.
 narrateur|Raphaël touche le bouton du manteau.</t>
         </is>
@@ -2096,10 +2102,13 @@
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On prend le manteau.
-papa|Bravo. Tu as pris le manteau.
+          <t>narrateur|Oui.
+narrateur|On prend le manteau.
+papa|Bravo.
+papa|Tu as pris le manteau.
 maman|En rentrant, on le raccroche.
-narrateur|Raphaël respire. Ça sent la soupe.</t>
+narrateur|Raphaël respire.
+narrateur|Ça sent la soupe.</t>
         </is>
       </c>
     </row>
@@ -2126,7 +2135,7 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>Tu emportes quel jeu ? On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu emportes quel jeu ? Les cubes. Le livre. Ou la dînette.</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -2295,7 +2304,9 @@
       <c r="AW7" t="inlineStr">
         <is>
           <t>maman|Tu emportes quel jeu ?
-narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+narrateur|Les cubes.
+narrateur|Le livre.
+narrateur|Ou la dînette.</t>
         </is>
       </c>
     </row>
@@ -2463,12 +2474,17 @@
       <c r="AW8" t="inlineStr">
         <is>
           <t>narrateur|Raphaël a choisi les cubes.
-narrateur|Ils sont en bois. Ils cliquent.
+narrateur|Ils sont en bois.
+narrateur|Ils cliquent.
 narrateur|Un vélo passe au loin.
-papa|On prend les cubes. Et le manteau reste mis.
+papa|On prend les cubes.
+papa|Et le manteau reste mis.
 maman|Tu as ton manteau ?
-enfant-m|Oui. Il est chaud.
-papa|Bravo. On sort. Puis on rentre.
+enfant-m|Oui.
+enfant-m|Il est chaud.
+papa|Bravo.
+papa|On sort.
+papa|Puis on rentre.
 narrateur|Les cubes sont dans une boîte lisse.</t>
         </is>
       </c>
@@ -2501,7 +2517,7 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -2670,7 +2686,9 @@
       <c r="AW9" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -2697,7 +2715,7 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Une miette reste sur la table. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
@@ -2840,18 +2858,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Une miette reste sur la table.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -2878,7 +2903,7 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Une miette reste sur la table. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
@@ -3023,8 +3048,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Une miette reste sur la table.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -3052,7 +3079,7 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. La casserole fait un tout petit pschitt. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
@@ -3195,18 +3222,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|La casserole fait un tout petit pschitt.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -3233,7 +3267,7 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. La casserole fait un tout petit pschitt. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -3378,8 +3412,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|La casserole fait un tout petit pschitt.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -3407,7 +3443,7 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. La vitre de cuisine a une goutte. Les cubes sont rangés dans la boîte. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -3550,18 +3586,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|La vitre de cuisine a une goutte.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -3588,7 +3631,7 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. La vitre de cuisine a une goutte. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
@@ -3733,8 +3776,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|La vitre de cuisine a une goutte.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -3905,10 +3950,12 @@
           <t>narrateur|Raphaël a choisi le livre.
 narrateur|Les pages sentent le papier.
 narrateur|La lumière de la cuisine est claire.
-maman|Le livre vient. Le manteau aussi.
+maman|Le livre vient.
+maman|Le manteau aussi.
 papa|Tu as pris le manteau avant de sortir.
 enfant-m|Oui, papa.
-maman|Bravo. En rentrant, on raccroche.
+maman|Bravo.
+maman|En rentrant, on raccroche.
 narrateur|Raphaël souffle sur une page.</t>
         </is>
       </c>
@@ -3936,7 +3983,7 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -4105,7 +4152,9 @@
       <c r="AW17" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -4132,7 +4181,7 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Un cube sent le bois clair. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
@@ -4275,18 +4324,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Un cube sent le bois clair.
 narrateur|Le livre est fermé, tout sage.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -4313,7 +4369,7 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Un cube sent le bois clair. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
@@ -4458,8 +4514,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Un cube sent le bois clair.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -4487,7 +4545,7 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Une page se recourbe un peu. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
@@ -4630,18 +4688,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Une page se recourbe un peu.
 narrateur|Le livre est fermé, tout sage.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -4668,7 +4733,7 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Une page se recourbe un peu. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
@@ -4813,8 +4878,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Une page se recourbe un peu.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -4842,7 +4909,7 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Une tasse tremble près de l'évier. Le livre est fermé, tout sage. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
@@ -4985,18 +5052,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Une tasse tremble près de l'évier.
 narrateur|Le livre est fermé, tout sage.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -5023,7 +5097,7 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Une tasse tremble près de l'évier. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
@@ -5168,8 +5242,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Une tasse tremble près de l'évier.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -5197,7 +5273,7 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>Raphaël a choisi la dînette. Les petites tasses sont lisses. Ça sent encore la soupe. On emporte la dînette. Le manteau est bien mis. Bravo. Je sors avec. Puis on rentre. On raccroche le manteau. Une tasse fait un tout petit ting.</t>
+          <t>Raphaël a choisi la dînette. Les petites tasses sont lisses. Ça sent encore la soupe. On emporte la dînette. Le manteau est bien mis. Bravo. Je sors avec le manteau. Puis on rentre. On raccroche le manteau. Une tasse fait un tout petit ting.</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
@@ -5341,9 +5417,11 @@
 narrateur|Les petites tasses sont lisses.
 narrateur|Ça sent encore la soupe.
 papa|On emporte la dînette.
-maman|Le manteau est bien mis. Bravo.
-enfant-m|Je sors avec.
-papa|Puis on rentre. On raccroche le manteau.
+maman|Le manteau est bien mis.
+maman|Bravo.
+enfant-m|Je sors avec le manteau.
+papa|Puis on rentre.
+papa|On raccroche le manteau.
 narrateur|Une tasse fait un tout petit ting.</t>
         </is>
       </c>
@@ -5371,7 +5449,7 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
@@ -5540,7 +5618,9 @@
       <c r="AW25" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -5567,7 +5647,7 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Une goutte tombe de la gouttière. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
@@ -5710,18 +5790,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Une goutte tombe de la gouttière.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -5748,7 +5835,7 @@
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Une goutte tombe de la gouttière. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
@@ -5893,8 +5980,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Une goutte tombe de la gouttière.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -5922,7 +6011,7 @@
       </c>
       <c r="E28" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. L'herbe colle aux bottes jaunes. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F28" s="2" t="inlineStr">
@@ -6065,18 +6154,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|L'herbe colle aux bottes jaunes.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -6103,7 +6199,7 @@
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. L'herbe colle aux bottes jaunes. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
@@ -6248,8 +6344,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|L'herbe colle aux bottes jaunes.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -6277,7 +6375,7 @@
       </c>
       <c r="E30" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Un ver de terre recule tout doux. Les tasses de la dînette sont empilées. La cuisine sent encore la soupe. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F30" s="2" t="inlineStr">
@@ -6420,18 +6518,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Un ver de terre recule tout doux.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|La cuisine sent encore la soupe.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -6458,7 +6563,7 @@
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la cuisine. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Un ver de terre recule tout doux. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
@@ -6603,8 +6708,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Un ver de terre recule tout doux.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -6632,7 +6739,7 @@
       </c>
       <c r="E32" s="2" t="inlineStr">
         <is>
-          <t>Raphaël va vers le jardin. L'herbe est mouillée, toute brillante. L'air est frais sur le nez. Le manteau sent la laine. On a pris le manteau avant de sortir. Bravo, Raphaël. J'ai pas froid. Une goutte tombe d'une feuille. Elle fait un tout petit bruit. Quand on rentre, on raccroche le manteau. Raphaël serre le col contre sa joue.</t>
+          <t>Raphaël va vers le jardin. L'herbe est mouillée, toute brillante. L'air est frais sur le nez. Le manteau sent la laine. On a pris le manteau avant de sortir. Bravo, Raphaël. Je n'ai pas froid. Une goutte tombe d'une feuille. Elle fait un tout petit bruit. Quand on rentre, on raccroche le manteau. Raphaël serre le col contre sa joue.</t>
         </is>
       </c>
       <c r="F32" s="2" t="inlineStr">
@@ -6778,7 +6885,7 @@
 narrateur|Le manteau sent la laine.
 papa|On a pris le manteau avant de sortir.
 maman|Bravo, Raphaël.
-enfant-m|J'ai pas froid.
+enfant-m|Je n'ai pas froid.
 narrateur|Une goutte tombe d'une feuille.
 narrateur|Elle fait un tout petit bruit.
 papa|Quand on rentre, on raccroche le manteau.
@@ -7140,9 +7247,12 @@
       </c>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>narrateur|Oui. On prend le manteau avant de sortir.
-maman|Bravo, Raphaël. Bon travail.
-papa|Puis on rentre. On raccroche.
+          <t>narrateur|Oui.
+narrateur|On prend le manteau avant de sortir.
+maman|Bravo, Raphaël.
+maman|Bon travail.
+papa|Puis on rentre.
+papa|On raccroche.
 narrateur|L'herbe mouillée brille encore.</t>
         </is>
       </c>
@@ -7170,7 +7280,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>Tu emportes quel jeu ? On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu emportes quel jeu ? Les cubes. Le livre. Ou la dînette.</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -7339,7 +7449,9 @@
       <c r="AW35" t="inlineStr">
         <is>
           <t>maman|Tu emportes quel jeu ?
-narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+narrateur|Les cubes.
+narrateur|Le livre.
+narrateur|Ou la dînette.</t>
         </is>
       </c>
     </row>
@@ -7509,8 +7621,10 @@
           <t>narrateur|Raphaël a choisi les cubes, dans le jardin.
 narrateur|Un chat miaule une fois.
 narrateur|Les cubes sont un peu froids.
-papa|On joue. Le manteau reste sur toi.
-maman|Tu l'as pris avant de sortir. Bravo.
+papa|On joue.
+papa|Le manteau reste sur toi.
+maman|Tu l'as pris avant de sortir.
+maman|Bravo.
 enfant-m|Les cubes font clic.
 papa|Quand on rentre, on raccroche.
 narrateur|L'herbe mouille le bas du manteau.</t>
@@ -7540,7 +7654,7 @@
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
@@ -7709,7 +7823,9 @@
       <c r="AW37" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -7736,7 +7852,7 @@
       </c>
       <c r="E38" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont froids comme l'air. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F38" s="2" t="inlineStr">
@@ -7879,18 +7995,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Les cubes sont froids comme l'air.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -7917,7 +8040,7 @@
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Les cubes sont froids comme l'air. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
@@ -8062,8 +8185,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Les cubes sont froids comme l'air.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -8091,7 +8216,7 @@
       </c>
       <c r="E40" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre a une tache de pluie. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F40" s="2" t="inlineStr">
@@ -8234,18 +8359,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le livre a une tache de pluie.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -8272,7 +8404,7 @@
       </c>
       <c r="E41" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le livre a une tache de pluie. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F41" s="2" t="inlineStr">
@@ -8417,8 +8549,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le livre a une tache de pluie.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -8446,7 +8580,7 @@
       </c>
       <c r="E42" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Une tasse se renverse dans l'herbe. Les cubes sont rangés dans la boîte. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F42" s="2" t="inlineStr">
@@ -8589,18 +8723,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Une tasse se renverse dans l'herbe.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -8627,7 +8768,7 @@
       </c>
       <c r="E43" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Une tasse se renverse dans l'herbe. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F43" s="2" t="inlineStr">
@@ -8772,8 +8913,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Une tasse se renverse dans l'herbe.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -8946,8 +9089,10 @@
 maman|On met le livre à l'abri.
 papa|Le manteau te tient chaud.
 enfant-m|Il est rêche et chaud.
-maman|Bravo. Tu as pris le manteau.
-papa|On rentre bientôt. On raccroche.
+maman|Bravo.
+maman|Tu as pris le manteau.
+papa|On rentre bientôt.
+papa|On raccroche.
 narrateur|Raphaël tient le livre contre lui.</t>
         </is>
       </c>
@@ -8975,7 +9120,7 @@
       </c>
       <c r="E45" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F45" s="2" t="inlineStr">
@@ -9144,7 +9289,9 @@
       <c r="AW45" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -9171,7 +9318,7 @@
       </c>
       <c r="E46" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le rideau de la chambre frémit. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F46" s="2" t="inlineStr">
@@ -9314,18 +9461,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le rideau de la chambre frémit.
 narrateur|Le livre est fermé, tout sage.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -9352,7 +9506,7 @@
       </c>
       <c r="E47" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le rideau de la chambre frémit. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F47" s="2" t="inlineStr">
@@ -9497,8 +9651,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le rideau de la chambre frémit.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -9526,7 +9682,7 @@
       </c>
       <c r="E48" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. L'oreiller garde un creux rond. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F48" s="2" t="inlineStr">
@@ -9669,18 +9825,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|L'oreiller garde un creux rond.
 narrateur|Le livre est fermé, tout sage.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -9707,7 +9870,7 @@
       </c>
       <c r="E49" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. L'oreiller garde un creux rond. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F49" s="2" t="inlineStr">
@@ -9852,8 +10015,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|L'oreiller garde un creux rond.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -9881,7 +10046,7 @@
       </c>
       <c r="E50" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. L'armoire craque une fois. Le livre est fermé, tout sage. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F50" s="2" t="inlineStr">
@@ -10024,18 +10189,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|L'armoire craque une fois.
 narrateur|Le livre est fermé, tout sage.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -10062,7 +10234,7 @@
       </c>
       <c r="E51" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. L'armoire craque une fois. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F51" s="2" t="inlineStr">
@@ -10207,8 +10379,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|L'armoire craque une fois.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -10379,9 +10553,11 @@
           <t>narrateur|Raphaël a choisi la dînette, dans l'herbe.
 narrateur|Les petites assiettes sont froides.
 papa|On fait un goûter de jardin.
-maman|Tu as ton manteau. C'est bien.
+maman|Tu as ton manteau.
+maman|C'est bien.
 enfant-m|Je sers l'eau.
-papa|Bravo. Après, on rentre.
+papa|Bravo.
+papa|Après, on rentre.
 maman|Et on raccroche le manteau.
 narrateur|Une tasse tremble dans l'herbe.</t>
         </is>
@@ -10410,7 +10586,7 @@
       </c>
       <c r="E53" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F53" s="2" t="inlineStr">
@@ -10579,7 +10755,9 @@
       <c r="AW53" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -10606,7 +10784,7 @@
       </c>
       <c r="E54" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Un cube rouge se cache. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F54" s="2" t="inlineStr">
@@ -10749,18 +10927,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Un cube rouge se cache.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -10787,7 +10972,7 @@
       </c>
       <c r="E55" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Un cube rouge se cache. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F55" s="2" t="inlineStr">
@@ -10932,8 +11117,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Un cube rouge se cache.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -10961,7 +11148,7 @@
       </c>
       <c r="E56" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre sent encore le savon. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F56" s="2" t="inlineStr">
@@ -11104,18 +11291,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le livre sent encore le savon.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -11142,7 +11336,7 @@
       </c>
       <c r="E57" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le livre sent encore le savon. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F57" s="2" t="inlineStr">
@@ -11287,8 +11481,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le livre sent encore le savon.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -11316,7 +11512,7 @@
       </c>
       <c r="E58" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses font un petit ting. Les tasses de la dînette sont empilées. L'herbe du jardin brille dans la lumière. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F58" s="2" t="inlineStr">
@@ -11459,18 +11655,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Les tasses font un petit ting.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|L'herbe du jardin brille dans la lumière.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -11497,7 +11700,7 @@
       </c>
       <c r="E59" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par le jardin. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Les tasses font un petit ting. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F59" s="2" t="inlineStr">
@@ -11642,8 +11845,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Les tasses font un petit ting.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -11815,12 +12020,14 @@
 narrateur|La couverture est douce, toute pliée.
 narrateur|Le rideau bouge un peu.
 narrateur|Le manteau frotte la porte.
-maman|Tu as pris le manteau. C'est bien.
+maman|Tu as pris le manteau.
+maman|C'est bien.
 papa|Avant de sortir, on le met.
 enfant-m|Il est sur moi.
 narrateur|L'oreiller sent le savon.
 papa|On sort un moment.
-maman|Puis on rentre. Et on raccroche.
+maman|Puis on rentre.
+maman|Et on raccroche.
 narrateur|Raphaël marche tout doux sur le tapis.</t>
         </is>
       </c>
@@ -12179,10 +12386,13 @@
       </c>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>narrateur|Oui. Raphaël a pris le manteau.
-papa|C'est ça. Bravo.
+          <t>narrateur|Oui.
+narrateur|Raphaël a pris le manteau.
+papa|C'est ça.
+papa|Bravo.
 maman|Le manteau se raccroche, en rentrant.
-narrateur|La chambre est calme. Le rideau se tait.</t>
+narrateur|La chambre est calme.
+narrateur|Le rideau se tait.</t>
         </is>
       </c>
     </row>
@@ -12209,7 +12419,7 @@
       </c>
       <c r="E63" s="2" t="inlineStr">
         <is>
-          <t>Tu emportes quel jeu ? On peut prendre les cubes, le livre, ou la dînette.</t>
+          <t>Tu emportes quel jeu ? Les cubes. Le livre. Ou la dînette.</t>
         </is>
       </c>
       <c r="F63" s="2" t="inlineStr">
@@ -12378,7 +12588,9 @@
       <c r="AW63" t="inlineStr">
         <is>
           <t>maman|Tu emportes quel jeu ?
-narrateur|On peut prendre les cubes, le livre, ou la dînette.</t>
+narrateur|Les cubes.
+narrateur|Le livre.
+narrateur|Ou la dînette.</t>
         </is>
       </c>
     </row>
@@ -12547,7 +12759,8 @@
         <is>
           <t>narrateur|Raphaël a choisi les cubes, dans la chambre.
 narrateur|Ils cliquent sur le tapis épais.
-maman|On joue un peu. Puis on sort.
+maman|On joue un peu.
+maman|Puis on sort.
 papa|Avant de sortir, le manteau est mis.
 enfant-m|Il est déjà sur moi.
 maman|Bravo, Raphaël.
@@ -12579,7 +12792,7 @@
       </c>
       <c r="E65" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F65" s="2" t="inlineStr">
@@ -12748,7 +12961,9 @@
       <c r="AW65" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12990,7 @@
       </c>
       <c r="E66" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le matin sent le pain. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F66" s="2" t="inlineStr">
@@ -12918,18 +13133,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le matin sent le pain.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -12956,7 +13178,7 @@
       </c>
       <c r="E67" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le matin sent le pain. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F67" s="2" t="inlineStr">
@@ -13101,8 +13323,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le matin sent le pain.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -13130,7 +13354,7 @@
       </c>
       <c r="E68" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Après la sieste, les joues brûlent. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F68" s="2" t="inlineStr">
@@ -13273,18 +13497,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Après la sieste, les joues brûlent.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -13311,7 +13542,7 @@
       </c>
       <c r="E69" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Après la sieste, les joues brûlent. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F69" s="2" t="inlineStr">
@@ -13456,8 +13687,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Après la sieste, les joues brûlent.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -13485,7 +13718,7 @@
       </c>
       <c r="E70" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le soir, la lampe ronronne. Les cubes sont rangés dans la boîte. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F70" s="2" t="inlineStr">
@@ -13628,18 +13861,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le soir, la lampe ronronne.
 narrateur|Les cubes sont rangés dans la boîte.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -13666,7 +13906,7 @@
       </c>
       <c r="E71" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec les cubes. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le soir, la lampe ronronne. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F71" s="2" t="inlineStr">
@@ -13811,8 +14051,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le soir, la lampe ronronne.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -13982,10 +14224,13 @@
         <is>
           <t>narrateur|Raphaël a choisi le livre, sur le lit.
 narrateur|La couverture est douce sous le livre.
-papa|On lit. Puis on sort.
-maman|Tu as pris le manteau. Bravo.
+papa|On lit.
+papa|Puis on sort.
+maman|Tu as pris le manteau.
+maman|Bravo.
 enfant-m|Les pages font frou frou.
-papa|On rentre après. On raccroche.
+papa|On rentre après.
+papa|On raccroche.
 narrateur|Raphaël touche une image lisse.</t>
         </is>
       </c>
@@ -14013,7 +14258,7 @@
       </c>
       <c r="E73" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F73" s="2" t="inlineStr">
@@ -14182,7 +14427,9 @@
       <c r="AW73" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -14209,7 +14456,7 @@
       </c>
       <c r="E74" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le crochet tapote le mur. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F74" s="2" t="inlineStr">
@@ -14352,18 +14599,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le crochet tapote le mur.
 narrateur|Le livre est fermé, tout sage.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -14390,7 +14644,7 @@
       </c>
       <c r="E75" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet tapote le mur. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F75" s="2" t="inlineStr">
@@ -14535,8 +14789,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le crochet tapote le mur.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -14564,7 +14820,7 @@
       </c>
       <c r="E76" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le manteau sèche un peu. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F76" s="2" t="inlineStr">
@@ -14707,18 +14963,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le manteau sèche un peu.
 narrateur|Le livre est fermé, tout sage.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -14745,7 +15008,7 @@
       </c>
       <c r="E77" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le manteau sèche un peu. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F77" s="2" t="inlineStr">
@@ -14890,8 +15153,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le manteau sèche un peu.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -14919,7 +15184,7 @@
       </c>
       <c r="E78" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Une botte laisse une trace. Le livre est fermé, tout sage. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F78" s="2" t="inlineStr">
@@ -15062,18 +15327,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Une botte laisse une trace.
 narrateur|Le livre est fermé, tout sage.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -15100,7 +15372,7 @@
       </c>
       <c r="E79" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec le livre. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Une botte laisse une trace. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F79" s="2" t="inlineStr">
@@ -15245,8 +15517,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Une botte laisse une trace.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -15416,11 +15690,15 @@
         <is>
           <t>narrateur|Raphaël a choisi la dînette, près de l'armoire.
 narrateur|Les tasses sont alignées, toutes petites.
-maman|On sert le thé. Puis on sort.
-papa|Le manteau est prêt. Il est sur toi.
+maman|On sert le thé.
+maman|Puis on sort.
+papa|Le manteau est prêt.
+papa|Il est sur toi.
 enfant-m|Je sers papa.
-maman|Bravo. Tu as pris le manteau.
-papa|Après, on rentre. On raccroche.
+maman|Bravo.
+maman|Tu as pris le manteau.
+papa|Après, on rentre.
+papa|On raccroche.
 narrateur|Ça sent le bois de l'armoire.</t>
         </is>
       </c>
@@ -15448,7 +15726,7 @@
       </c>
       <c r="E81" s="2" t="inlineStr">
         <is>
-          <t>C'est quel moment, pour sortir ? On peut prendre le matin, après la sieste, ou le soir.</t>
+          <t>C'est quel moment, pour sortir ? Le matin. Après la sieste. Ou le soir.</t>
         </is>
       </c>
       <c r="F81" s="2" t="inlineStr">
@@ -15617,7 +15895,9 @@
       <c r="AW81" t="inlineStr">
         <is>
           <t>papa|C'est quel moment, pour sortir ?
-narrateur|On peut prendre le matin, après la sieste, ou le soir.</t>
+narrateur|Le matin.
+narrateur|Après la sieste.
+narrateur|Ou le soir.</t>
         </is>
       </c>
     </row>
@@ -15644,7 +15924,7 @@
       </c>
       <c r="E82" s="2" t="inlineStr">
         <is>
-          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le matin. La lumière est pâle, tout douce. Un oiseau chante une fois. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le tapis du salon est chaud. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F82" s="2" t="inlineStr">
@@ -15787,18 +16067,25 @@
           <t>narrateur|C'est le matin.
 narrateur|La lumière est pâle, tout douce.
 narrateur|Un oiseau chante une fois.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le tapis du salon est chaud.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -15825,7 +16112,7 @@
       </c>
       <c r="E83" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était le matin. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le tapis du salon est chaud. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F83" s="2" t="inlineStr">
@@ -15970,8 +16257,10 @@
 narrateur|C'était le matin.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le tapis du salon est chaud.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -15999,7 +16288,7 @@
       </c>
       <c r="E84" s="2" t="inlineStr">
         <is>
-          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est après la sieste. Les joues de Raphaël sont chaudes. La maison est encore calme. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. La chaussette est encore sous le canapé. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F84" s="2" t="inlineStr">
@@ -16142,18 +16431,25 @@
           <t>narrateur|C'est après la sieste.
 narrateur|Les joues de Raphaël sont chaudes.
 narrateur|La maison est encore calme.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|La chaussette est encore sous le canapé.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -16180,7 +16476,7 @@
       </c>
       <c r="E85" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était après la sieste. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. La chaussette est encore sous le canapé. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F85" s="2" t="inlineStr">
@@ -16325,8 +16621,10 @@
 narrateur|C'était après la sieste.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|La chaussette est encore sous le canapé.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -16354,7 +16652,7 @@
       </c>
       <c r="E86" s="2" t="inlineStr">
         <is>
-          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
+          <t>C'est le soir. La lampe fait un rond orange. Les ombres sont longues sur le tapis. On sort. Tu as ton manteau ? Oui. Je l'ai pris. Bravo. C'est le bon geste. Ils sortent un moment. L'air touche le nez de Raphaël. C'est l'heure de rentrer. Ils rentrent. Raphaël retire le manteau. Il le raccroche au petit crochet. Le manteau est à sa place. Bravo. Le radiateur fait encore tic tic. Les tasses de la dînette sont empilées. La chambre garde l'odeur de l'oreiller. Merci, Raphaël. Tu as fait du bon travail.</t>
         </is>
       </c>
       <c r="F86" s="2" t="inlineStr">
@@ -16497,18 +16795,25 @@
           <t>narrateur|C'est le soir.
 narrateur|La lampe fait un rond orange.
 narrateur|Les ombres sont longues sur le tapis.
-papa|On sort. Tu as ton manteau ?
-enfant-m|Oui. Je l'ai pris.
-maman|Bravo. C'est le bon geste.
+papa|On sort.
+papa|Tu as ton manteau ?
+enfant-m|Oui.
+enfant-m|Je l'ai pris.
+maman|Bravo.
+maman|C'est le bon geste.
 narrateur|Ils sortent un moment.
 narrateur|L'air touche le nez de Raphaël.
 papa|C'est l'heure de rentrer.
-narrateur|Ils rentrent. Raphaël retire le manteau.
+narrateur|Ils rentrent.
+narrateur|Raphaël retire le manteau.
 narrateur|Il le raccroche au petit crochet.
-maman|Le manteau est à sa place. Bravo.
+maman|Le manteau est à sa place.
+maman|Bravo.
+narrateur|Le radiateur fait encore tic tic.
 narrateur|Les tasses de la dînette sont empilées.
 narrateur|La chambre garde l'odeur de l'oreiller.
-papa|Merci, Raphaël. Tu as fait du bon travail.</t>
+papa|Merci, Raphaël.
+papa|Tu as fait du bon travail.</t>
         </is>
       </c>
     </row>
@@ -16535,7 +16840,7 @@
       </c>
       <c r="E87" s="2" t="inlineStr">
         <is>
-          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
+          <t>Raphaël est passé par la chambre. Il a joué avec la dînette. C'était le soir. Il a pris le manteau avant de sortir. En rentrant, il l'a raccroché. Le radiateur fait encore tic tic. Le crochet attend déjà demain. Bravo. On est rentrés. L'histoire est finie.</t>
         </is>
       </c>
       <c r="F87" s="2" t="inlineStr">
@@ -16680,8 +16985,10 @@
 narrateur|C'était le soir.
 narrateur|Il a pris le manteau avant de sortir.
 narrateur|En rentrant, il l'a raccroché.
+narrateur|Le radiateur fait encore tic tic.
 maman|Le crochet attend déjà demain.
-papa|Bravo. On est rentrés.
+papa|Bravo.
+papa|On est rentrés.
 narrateur|L'histoire est finie.</t>
         </is>
       </c>
@@ -16703,7 +17010,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A6"/>
+  <dimension ref="A1:A9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -16746,6 +17053,27 @@
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>F-NAR-009 ouverture du monde, fusion agents</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
         <is>
           <t>F-NAR-009 ouverture du monde, fusion agents</t>
         </is>
